--- a/results/04-2026/beta/inputs-04-2026.xlsx
+++ b/results/04-2026/beta/inputs-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -248,12 +248,12 @@
     <t xml:space="preserve">2026 Q1</t>
   </si>
   <si>
+    <t xml:space="preserve">2026 Q2</t>
+  </si>
+  <si>
     <t xml:space="preserve">projection</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 Q2</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 Q3</t>
   </si>
   <si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t xml:space="preserve">2027 Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028 Q1</t>
   </si>
 </sst>
 </file>
@@ -4452,7 +4455,7 @@
         <v>110.469375919111</v>
       </c>
       <c r="U25" t="n">
-        <v>163.113202913515</v>
+        <v>186.3</v>
       </c>
       <c r="V25" t="n">
         <v>2375.939</v>
@@ -4485,7 +4488,7 @@
         <v>0.49</v>
       </c>
       <c r="AF25" t="n">
-        <v>-8.05545</v>
+        <v>-8.046285</v>
       </c>
       <c r="AG25" t="n">
         <v>0.7</v>
@@ -4506,7 +4509,7 @@
         <v>-175.933333333333</v>
       </c>
       <c r="AM25" t="n">
-        <v>-69.0204400971171</v>
+        <v>-69.7933333333333</v>
       </c>
       <c r="AN25" t="n">
         <v>2130.824925</v>
@@ -4536,7 +4539,7 @@
         <v>2.04112</v>
       </c>
       <c r="AW25" t="n">
-        <v>-1.473395937</v>
+        <v>-1.471562937</v>
       </c>
       <c r="AX25" t="n">
         <v>0.315</v>
@@ -4553,55 +4556,55 @@
         <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0206881991200681</v>
+        <v>-0.014341822054897</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00825837924065231</v>
+        <v>0.0140339887996541</v>
       </c>
       <c r="F26" t="n">
-        <v>0.00825837924065231</v>
+        <v>0.0117801234585584</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00825837924065231</v>
+        <v>0.0135960722457957</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00925374721946359</v>
+        <v>0.0109906396255852</v>
       </c>
       <c r="I26" t="n">
         <v>0.00562340411235041</v>
       </c>
       <c r="J26" t="n">
-        <v>31819.4366967176</v>
+        <v>31856.3</v>
       </c>
       <c r="K26" t="n">
-        <v>21593.8580385309</v>
+        <v>21683.7</v>
       </c>
       <c r="L26" t="n">
         <v>0.06</v>
       </c>
       <c r="M26" t="n">
-        <v>2059.88109070427</v>
+        <v>1987.5</v>
       </c>
       <c r="N26" t="n">
-        <v>420.432960972294</v>
+        <v>416.5053188</v>
       </c>
       <c r="O26" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P26" t="n">
-        <v>3403.83361533309</v>
+        <v>3431</v>
       </c>
       <c r="Q26" t="n">
-        <v>5103.59064303823</v>
+        <v>5099.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2590.08236078972</v>
+        <v>2592.7</v>
       </c>
       <c r="S26" t="n">
         <v>445.021075130373</v>
@@ -4610,13 +4613,13 @@
         <v>135.971828422603</v>
       </c>
       <c r="U26" t="n">
-        <v>166.425523958362</v>
+        <v>178.918018791946</v>
       </c>
       <c r="V26" t="n">
-        <v>2440.18948581216</v>
+        <v>2394.7</v>
       </c>
       <c r="W26" t="n">
-        <v>226.552471112076</v>
+        <v>203.4</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -4628,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>35.7</v>
+        <v>36.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>95.9</v>
+        <v>133.9</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4643,34 +4646,34 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>-8.01832</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AH26" t="n">
-        <v>2000.49031793371</v>
+        <v>2012.824</v>
       </c>
       <c r="AI26" t="n">
-        <v>343.950755680523</v>
+        <v>342.676</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-2928.91087716459</v>
+        <v>-2928.42</v>
       </c>
       <c r="AK26" t="n">
-        <v>-1499.51188329477</v>
+        <v>-1499.826</v>
       </c>
       <c r="AL26" t="n">
         <v>-176.794035837679</v>
       </c>
       <c r="AM26" t="n">
-        <v>-68.7712908957292</v>
+        <v>-69.9606006263981</v>
       </c>
       <c r="AN26" t="n">
-        <v>2159.48800930774</v>
+        <v>2149.252875</v>
       </c>
       <c r="AO26" t="n">
-        <v>188.921806000217</v>
+        <v>183.7125</v>
       </c>
       <c r="AP26" t="n">
         <v>0</v>
@@ -4682,10 +4685,10 @@
         <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>34.009</v>
+        <v>34.169</v>
       </c>
       <c r="AT26" t="n">
-        <v>46.33065</v>
+        <v>48.21165</v>
       </c>
       <c r="AU26" t="n">
         <v>0.378236</v>
@@ -4694,24 +4697,24 @@
         <v>1.53068</v>
       </c>
       <c r="AW26" t="n">
-        <v>-3.195359969</v>
+        <v>-1.590137919</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.28035</v>
+        <v>0.315</v>
       </c>
       <c r="AY26" t="n">
-        <v>1752.77459653508</v>
+        <v>1755.549675</v>
       </c>
       <c r="AZ26" t="n">
-        <v>304.724645028118</v>
+        <v>304.437825</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
         <v>79</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -4735,31 +4738,31 @@
         <v>0.00525368446989161</v>
       </c>
       <c r="J27" t="n">
-        <v>32195.2074487783</v>
+        <v>32232.5060882148</v>
       </c>
       <c r="K27" t="n">
-        <v>21864.3303317936</v>
+        <v>21955.2976021958</v>
       </c>
       <c r="L27" t="n">
         <v>0.06</v>
       </c>
       <c r="M27" t="n">
-        <v>2053.06517714637</v>
+        <v>1993.92358728499</v>
       </c>
       <c r="N27" t="n">
-        <v>420.487484759299</v>
+        <v>416.521141931903</v>
       </c>
       <c r="O27" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P27" t="n">
-        <v>3436.32310057099</v>
+        <v>3463.7487875286</v>
       </c>
       <c r="Q27" t="n">
-        <v>5141.84220000571</v>
+        <v>5117.7343736848</v>
       </c>
       <c r="R27" t="n">
-        <v>2623.27416515155</v>
+        <v>2626.36869158331</v>
       </c>
       <c r="S27" t="n">
         <v>432.67747940975</v>
@@ -4768,10 +4771,10 @@
         <v>156.945251003532</v>
       </c>
       <c r="U27" t="n">
-        <v>166.941911087545</v>
+        <v>179.473167785235</v>
       </c>
       <c r="V27" t="n">
-        <v>2461.57530742837</v>
+        <v>2429.67633142837</v>
       </c>
       <c r="W27" t="n">
         <v>229.826917122492</v>
@@ -4789,7 +4792,7 @@
         <v>35.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.9</v>
+        <v>133.9</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4801,34 +4804,34 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>-7.98307</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2045.13597114694</v>
+        <v>2042.95805853092</v>
       </c>
       <c r="AI27" t="n">
-        <v>346.556866325306</v>
+        <v>348.008366328366</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-2968.76194116527</v>
+        <v>-2965.37812484218</v>
       </c>
       <c r="AK27" t="n">
-        <v>-1518.37278311295</v>
+        <v>-1519.05824299</v>
       </c>
       <c r="AL27" t="n">
         <v>-177.366618484671</v>
       </c>
       <c r="AM27" t="n">
-        <v>-68.6626879319807</v>
+        <v>-70.2697062192393</v>
       </c>
       <c r="AN27" t="n">
-        <v>2171.16040347912</v>
+        <v>2153.74799957138</v>
       </c>
       <c r="AO27" t="n">
-        <v>194.845362352778</v>
+        <v>189.636056352561</v>
       </c>
       <c r="AP27" t="n">
         <v>0</v>
@@ -4840,10 +4843,10 @@
         <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>33.732</v>
+        <v>33.868</v>
       </c>
       <c r="AT27" t="n">
-        <v>45.7848</v>
+        <v>49.2903</v>
       </c>
       <c r="AU27" t="n">
         <v>0.211344</v>
@@ -4852,16 +4855,16 @@
         <v>1.05376</v>
       </c>
       <c r="AW27" t="n">
-        <v>-4.807197548</v>
+        <v>-1.846002748</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.250425</v>
+        <v>0.28035</v>
       </c>
       <c r="AY27" t="n">
-        <v>1790.45669004314</v>
+        <v>1792.74173816946</v>
       </c>
       <c r="AZ27" t="n">
-        <v>310.893439951312</v>
+        <v>310.933207423882</v>
       </c>
     </row>
     <row r="28">
@@ -4869,7 +4872,7 @@
         <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -4893,31 +4896,31 @@
         <v>0.00537994009364007</v>
       </c>
       <c r="J28" t="n">
-        <v>32569.7744504319</v>
+        <v>32607.5070314593</v>
       </c>
       <c r="K28" t="n">
-        <v>22112.0376229908</v>
+        <v>22204.0354877811</v>
       </c>
       <c r="L28" t="n">
         <v>0.06</v>
       </c>
       <c r="M28" t="n">
-        <v>2069.1207329875</v>
+        <v>2009.51663900832</v>
       </c>
       <c r="N28" t="n">
-        <v>424.373164889901</v>
+        <v>420.367740074114</v>
       </c>
       <c r="O28" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P28" t="n">
-        <v>3469.5651322408</v>
+        <v>3497.25612764809</v>
       </c>
       <c r="Q28" t="n">
-        <v>5180.45144191064</v>
+        <v>5156.07541767194</v>
       </c>
       <c r="R28" t="n">
-        <v>2653.17809426072</v>
+        <v>2656.13677457201</v>
       </c>
       <c r="S28" t="n">
         <v>420.676259283967</v>
@@ -4926,10 +4929,10 @@
         <v>164.885835526837</v>
       </c>
       <c r="U28" t="n">
-        <v>167.560645215304</v>
+        <v>180.138346308725</v>
       </c>
       <c r="V28" t="n">
-        <v>2484.800976</v>
+        <v>2452.902</v>
       </c>
       <c r="W28" t="n">
         <v>233.148689902827</v>
@@ -4947,7 +4950,7 @@
         <v>35.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>95.9</v>
+        <v>133.9</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4959,34 +4962,34 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2090.69035010388</v>
+        <v>2088.12338505647</v>
       </c>
       <c r="AI28" t="n">
-        <v>352.42918253682</v>
+        <v>353.222696367226</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-3012.59867561225</v>
+        <v>-3006.53517496281</v>
       </c>
       <c r="AK28" t="n">
-        <v>-1537.34321277686</v>
+        <v>-1538.22665593864</v>
       </c>
       <c r="AL28" t="n">
         <v>-177.109160460803</v>
       </c>
       <c r="AM28" t="n">
-        <v>-68.6313761058242</v>
+        <v>-70.6576510961968</v>
       </c>
       <c r="AN28" t="n">
-        <v>2196.56357307912</v>
+        <v>2171.97389957138</v>
       </c>
       <c r="AO28" t="n">
-        <v>201.403817580914</v>
+        <v>196.194511580697</v>
       </c>
       <c r="AP28" t="n">
         <v>0</v>
@@ -4998,10 +5001,10 @@
         <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>33.378</v>
+        <v>33.506</v>
       </c>
       <c r="AT28" t="n">
-        <v>45.3474</v>
+        <v>50.3919</v>
       </c>
       <c r="AU28" t="n">
         <v>-0.00499800000000003</v>
@@ -5010,16 +5013,16 @@
         <v>0.61906</v>
       </c>
       <c r="AW28" t="n">
-        <v>-6.3774651</v>
+        <v>-1.53603725</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.222075</v>
+        <v>0.250425</v>
       </c>
       <c r="AY28" t="n">
-        <v>1825.05209381652</v>
+        <v>1826.75957480716</v>
       </c>
       <c r="AZ28" t="n">
-        <v>312.279931022096</v>
+        <v>312.498239106508</v>
       </c>
     </row>
     <row r="29">
@@ -5027,7 +5030,7 @@
         <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -5051,31 +5054,31 @@
         <v>0.00537181203616477</v>
       </c>
       <c r="J29" t="n">
-        <v>32915.8526924526</v>
+        <v>32953.9862104078</v>
       </c>
       <c r="K29" t="n">
-        <v>22345.4039657503</v>
+        <v>22438.3727589378</v>
       </c>
       <c r="L29" t="n">
         <v>0.06</v>
       </c>
       <c r="M29" t="n">
-        <v>2081.92308239744</v>
+        <v>2021.95019774054</v>
       </c>
       <c r="N29" t="n">
-        <v>426.2872788</v>
+        <v>422.242386905102</v>
       </c>
       <c r="O29" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P29" t="n">
-        <v>3500.19245981835</v>
+        <v>3528.12789542346</v>
       </c>
       <c r="Q29" t="n">
-        <v>5215.01053676584</v>
+        <v>5190.38689030448</v>
       </c>
       <c r="R29" t="n">
-        <v>2681.26535469851</v>
+        <v>2684.09748115581</v>
       </c>
       <c r="S29" t="n">
         <v>439.007918245637</v>
@@ -5084,10 +5087,10 @@
         <v>162.643016309613</v>
       </c>
       <c r="U29" t="n">
-        <v>168.612028018865</v>
+        <v>181.26864966443</v>
       </c>
       <c r="V29" t="n">
-        <v>2499.98486413911</v>
+        <v>2468.08588813911</v>
       </c>
       <c r="W29" t="n">
         <v>236.518473484257</v>
@@ -5105,7 +5108,7 @@
         <v>35.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>95.9</v>
+        <v>133.9</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5117,34 +5120,34 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2108.85967220783</v>
+        <v>2106.59987078557</v>
       </c>
       <c r="AI29" t="n">
-        <v>355.523898218419</v>
+        <v>355.865936362206</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-3054.47140802381</v>
+        <v>-3046.89953937826</v>
       </c>
       <c r="AK29" t="n">
-        <v>-1555.50260543158</v>
+        <v>-1556.54023218234</v>
       </c>
       <c r="AL29" t="n">
         <v>-176.986091068991</v>
       </c>
       <c r="AM29" t="n">
-        <v>-68.4951103731197</v>
+        <v>-70.9432727516778</v>
       </c>
       <c r="AN29" t="n">
-        <v>2224.47389251042</v>
+        <v>2192.70694940268</v>
       </c>
       <c r="AO29" t="n">
-        <v>208.360474114872</v>
+        <v>203.151168114654</v>
       </c>
       <c r="AP29" t="n">
         <v>0</v>
@@ -5156,10 +5159,10 @@
         <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>33.032</v>
+        <v>33.152</v>
       </c>
       <c r="AT29" t="n">
-        <v>45.191025</v>
+        <v>51.689025</v>
       </c>
       <c r="AU29" t="n">
         <v>-0.028203</v>
@@ -5168,16 +5171,16 @@
         <v>0.37618</v>
       </c>
       <c r="AW29" t="n">
-        <v>-7.422628014</v>
+        <v>-0.871763964</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.1953</v>
+        <v>0.222075</v>
       </c>
       <c r="AY29" t="n">
-        <v>1855.16467006328</v>
+        <v>1856.36369573392</v>
       </c>
       <c r="AZ29" t="n">
-        <v>314.65365812124</v>
+        <v>314.948924788005</v>
       </c>
     </row>
     <row r="30">
@@ -5185,7 +5188,7 @@
         <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -5209,31 +5212,31 @@
         <v>0.00535544010784861</v>
       </c>
       <c r="J30" t="n">
-        <v>33250.7962432082</v>
+        <v>33289.3177983815</v>
       </c>
       <c r="K30" t="n">
-        <v>22561.8219149016</v>
+        <v>22655.6911221334</v>
       </c>
       <c r="L30" t="n">
         <v>0.06</v>
       </c>
       <c r="M30" t="n">
-        <v>2093.59266997535</v>
+        <v>2033.28362552671</v>
       </c>
       <c r="N30" t="n">
-        <v>429.230106659185</v>
+        <v>425.1453588</v>
       </c>
       <c r="O30" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P30" t="n">
-        <v>3532.17204361704</v>
+        <v>3560.36271193125</v>
       </c>
       <c r="Q30" t="n">
-        <v>5461.66342114658</v>
+        <v>5447.69456827922</v>
       </c>
       <c r="R30" t="n">
-        <v>2706.89733945536</v>
+        <v>2709.61779256644</v>
       </c>
       <c r="S30" t="n">
         <v>443.111839208704</v>
@@ -5242,10 +5245,10 @@
         <v>143.140105616203</v>
       </c>
       <c r="U30" t="n">
-        <v>168.095640889683</v>
+        <v>180.713500671141</v>
       </c>
       <c r="V30" t="n">
-        <v>2561.72386175076</v>
+        <v>2520.06792730276</v>
       </c>
       <c r="W30" t="n">
         <v>239.93696178451</v>
@@ -5263,7 +5266,7 @@
         <v>36.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.9</v>
+        <v>133.9</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5275,31 +5278,31 @@
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2133.88160616389</v>
+        <v>2132.08617923157</v>
       </c>
       <c r="AI30" t="n">
-        <v>357.128934982079</v>
+        <v>356.859779384814</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-3116.38993204676</v>
+        <v>-3108.60436251145</v>
       </c>
       <c r="AK30" t="n">
-        <v>-1573.53360051058</v>
+        <v>-1574.72016081599</v>
       </c>
       <c r="AL30" t="n">
         <v>-176.013152375948</v>
       </c>
       <c r="AM30" t="n">
-        <v>-68.3249650694424</v>
+        <v>-71.1937227740491</v>
       </c>
       <c r="AN30" t="n">
-        <v>2251.8191270966</v>
+        <v>2220.9147330458</v>
       </c>
       <c r="AO30" t="n">
         <v>211.371984516169</v>
@@ -5314,10 +5317,10 @@
         <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>33.049</v>
+        <v>33.121</v>
       </c>
       <c r="AT30" t="n">
-        <v>45.0648</v>
+        <v>52.8453</v>
       </c>
       <c r="AU30" t="n">
         <v>-0.051408</v>
@@ -5326,16 +5329,16 @@
         <v>0.23798</v>
       </c>
       <c r="AW30" t="n">
-        <v>-8.441094968</v>
+        <v>-0.691527418</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.171675</v>
+        <v>0.1953</v>
       </c>
       <c r="AY30" t="n">
-        <v>1885.17770991507</v>
+        <v>1883.19768606102</v>
       </c>
       <c r="AZ30" t="n">
-        <v>317.61874846409</v>
+        <v>318.140275149588</v>
       </c>
     </row>
     <row r="31">
@@ -5343,7 +5346,7 @@
         <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -5367,31 +5370,31 @@
         <v>0.00531873576798692</v>
       </c>
       <c r="J31" t="n">
-        <v>33585.3385438282</v>
+        <v>33624.247671365</v>
       </c>
       <c r="K31" t="n">
-        <v>22770.1166694833</v>
+        <v>22864.8524939393</v>
       </c>
       <c r="L31" t="n">
         <v>0.06</v>
       </c>
       <c r="M31" t="n">
-        <v>2104.42637360595</v>
+        <v>2043.8052482434</v>
       </c>
       <c r="N31" t="n">
-        <v>432.201931397671</v>
+        <v>428.076934857179</v>
       </c>
       <c r="O31" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P31" t="n">
-        <v>3564.07426393388</v>
+        <v>3592.51954751041</v>
       </c>
       <c r="Q31" t="n">
-        <v>5497.60756713771</v>
+        <v>5483.42963386668</v>
       </c>
       <c r="R31" t="n">
-        <v>2732.58249785194</v>
+        <v>2735.18355114505</v>
       </c>
       <c r="S31" t="n">
         <v>447.254124325517</v>
@@ -5400,10 +5403,10 @@
         <v>115.322937925207</v>
       </c>
       <c r="U31" t="n">
-        <v>168.174727206765</v>
+        <v>180.798523489933</v>
       </c>
       <c r="V31" t="n">
-        <v>2585.29337444779</v>
+        <v>2543.63743999979</v>
       </c>
       <c r="W31" t="n">
         <v>243.404858750762</v>
@@ -5421,7 +5424,7 @@
         <v>37.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>95.9</v>
+        <v>133.9</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5433,31 +5436,31 @@
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2159.84164224401</v>
+        <v>2157.0933788699</v>
       </c>
       <c r="AI31" t="n">
-        <v>358.20499001022</v>
+        <v>358.739093739241</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-3167.67820789734</v>
+        <v>-3159.66870515718</v>
       </c>
       <c r="AK31" t="n">
-        <v>-1591.13757897091</v>
+        <v>-1592.46633808405</v>
       </c>
       <c r="AL31" t="n">
         <v>-174.411623186798</v>
       </c>
       <c r="AM31" t="n">
-        <v>-68.2441226430012</v>
+        <v>-71.5336735570469</v>
       </c>
       <c r="AN31" t="n">
-        <v>2279.65569217597</v>
+        <v>2246.55598247437</v>
       </c>
       <c r="AO31" t="n">
         <v>214.42702138253</v>
@@ -5472,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>33.299</v>
+        <v>33.339</v>
       </c>
       <c r="AT31" t="n">
-        <v>44.911125</v>
+        <v>53.974125</v>
       </c>
       <c r="AU31" t="n">
         <v>-0.074613</v>
@@ -5484,16 +5487,16 @@
         <v>0.11938</v>
       </c>
       <c r="AW31" t="n">
-        <v>-9.32523632</v>
+        <v>-0.72538577</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.14805</v>
+        <v>0.171675</v>
       </c>
       <c r="AY31" t="n">
-        <v>1910.98648591191</v>
+        <v>1908.87813313729</v>
       </c>
       <c r="AZ31" t="n">
-        <v>320.239576293196</v>
+        <v>320.554688817035</v>
       </c>
     </row>
     <row r="32">
@@ -5501,7 +5504,7 @@
         <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -5525,31 +5528,31 @@
         <v>0.00528246336028104</v>
       </c>
       <c r="J32" t="n">
-        <v>33925.1974087458</v>
+        <v>33964.5002679672</v>
       </c>
       <c r="K32" t="n">
-        <v>22989.7437819213</v>
+        <v>23085.3933722518</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2115.85467665075</v>
+        <v>2054.90434205558</v>
       </c>
       <c r="N32" t="n">
-        <v>435.203038733497</v>
+        <v>431.037396925078</v>
       </c>
       <c r="O32" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P32" t="n">
-        <v>3594.84139632715</v>
+        <v>3623.5322358997</v>
       </c>
       <c r="Q32" t="n">
-        <v>5533.82999096448</v>
+        <v>5519.44070620309</v>
       </c>
       <c r="R32" t="n">
-        <v>2759.32499748659</v>
+        <v>2761.80377090598</v>
       </c>
       <c r="S32" t="n">
         <v>451.435132230733</v>
@@ -5558,10 +5561,10 @@
         <v>85.0823596752584</v>
       </c>
       <c r="U32" t="n">
-        <v>167.960728937013</v>
+        <v>180.568461744966</v>
       </c>
       <c r="V32" t="n">
-        <v>2608.980326448</v>
+        <v>2567.324392</v>
       </c>
       <c r="W32" t="n">
         <v>246.922878504595</v>
@@ -5579,7 +5582,7 @@
         <v>38.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>95.9</v>
+        <v>133.9</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5597,25 +5600,25 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>2186.63413335035</v>
+        <v>2183.90946118689</v>
       </c>
       <c r="AI32" t="n">
-        <v>359.864216015273</v>
+        <v>360.222346635286</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-3199.70000154428</v>
+        <v>-3190.8019158048</v>
       </c>
       <c r="AK32" t="n">
-        <v>-1608.42673830197</v>
+        <v>-1609.88972303878</v>
       </c>
       <c r="AL32" t="n">
         <v>-173.106127594489</v>
       </c>
       <c r="AM32" t="n">
-        <v>-68.1728136075684</v>
+        <v>-71.8826222818791</v>
       </c>
       <c r="AN32" t="n">
-        <v>2307.59604602677</v>
+        <v>2272.30102067437</v>
       </c>
       <c r="AO32" t="n">
         <v>217.526213817928</v>
@@ -5630,10 +5633,10 @@
         <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>33.691</v>
+        <v>33.731</v>
       </c>
       <c r="AT32" t="n">
-        <v>44.7255</v>
+        <v>55.071</v>
       </c>
       <c r="AU32" t="n">
         <v>-0.097818</v>
@@ -5642,16 +5645,16 @@
         <v>0.0196</v>
       </c>
       <c r="AW32" t="n">
-        <v>-7.3922875</v>
+        <v>-0.3218514</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.124425</v>
+        <v>0.14805</v>
       </c>
       <c r="AY32" t="n">
-        <v>1932.57383714237</v>
+        <v>1930.43000026663</v>
       </c>
       <c r="AZ32" t="n">
-        <v>321.912458825848</v>
+        <v>322.129610127348</v>
       </c>
     </row>
     <row r="33">
@@ -5659,7 +5662,7 @@
         <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -5683,31 +5686,31 @@
         <v>0.00523852479905496</v>
       </c>
       <c r="J33" t="n">
-        <v>34265.2568987313</v>
+        <v>34304.9537220644</v>
       </c>
       <c r="K33" t="n">
-        <v>23207.3651673051</v>
+        <v>23303.9201786162</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2121.81729343446</v>
+        <v>2060.69519681232</v>
       </c>
       <c r="N33" t="n">
-        <v>438.2337172</v>
+        <v>434.027029629306</v>
       </c>
       <c r="O33" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P33" t="n">
-        <v>3625.47993960063</v>
+        <v>3654.41530888475</v>
       </c>
       <c r="Q33" t="n">
-        <v>5569.5600274024</v>
+        <v>5554.96361371836</v>
       </c>
       <c r="R33" t="n">
-        <v>2786.40387103665</v>
+        <v>2788.75455279793</v>
       </c>
       <c r="S33" t="n">
         <v>455.65522491159</v>
@@ -5716,10 +5719,10 @@
         <v>50.6890505411461</v>
       </c>
       <c r="U33" t="n">
-        <v>169.128415148048</v>
+        <v>181.823798657718</v>
       </c>
       <c r="V33" t="n">
-        <v>2611.14115899406</v>
+        <v>2569.48522454606</v>
       </c>
       <c r="W33" t="n">
         <v>250.491745489055</v>
@@ -5737,7 +5740,7 @@
         <v>39.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>95.9</v>
+        <v>133.9</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5755,25 +5758,25 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2200.1373504904</v>
+        <v>2198.34357500005</v>
       </c>
       <c r="AI33" t="n">
-        <v>366.438857267369</v>
+        <v>367.007979818939</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-3228.41675080431</v>
+        <v>-3218.617771419</v>
       </c>
       <c r="AK33" t="n">
-        <v>-1624.72425295526</v>
+        <v>-1626.31325630583</v>
       </c>
       <c r="AL33" t="n">
         <v>-171.341301758209</v>
       </c>
       <c r="AM33" t="n">
-        <v>-68.00376077917</v>
+        <v>-72.1367489038031</v>
       </c>
       <c r="AN33" t="n">
-        <v>2332.60621236914</v>
+        <v>2295.11587136594</v>
       </c>
       <c r="AO33" t="n">
         <v>220.670200019007</v>
@@ -5788,10 +5791,10 @@
         <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>34.267</v>
+        <v>34.299</v>
       </c>
       <c r="AT33" t="n">
-        <v>44.7408</v>
+        <v>56.3688</v>
       </c>
       <c r="AU33" t="n">
         <v>-0.082501</v>
@@ -5800,16 +5803,174 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>-5.6698863</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
+        <v>0.124425</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1951.07233371489</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>324.636569905113</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.00514502687483964</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.00748128782640833</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.00748128782640833</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.00748128782640833</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00542041536348359</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.00520317743921583</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34647.4157511121</v>
+      </c>
+      <c r="K34" t="n">
+        <v>23529.8990511885</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2064.47645564375</v>
+      </c>
+      <c r="N34" t="n">
+        <v>437.0461204</v>
+      </c>
+      <c r="O34" t="n">
+        <v>75.1961428571429</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3685.16965313856</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5638.71752992768</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2816.33443957647</v>
+      </c>
+      <c r="S34" t="n">
+        <v>459.914767739242</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>181.533720805369</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2594.4113965679</v>
+      </c>
+      <c r="W34" t="n">
+        <v>254.112194617826</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2211.92489165399</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>375.061936771887</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>-3258.12743263814</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>-1643.00316280064</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>-171.031794016184</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>-72.041206263982</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2311.84315195059</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>223.859627406503</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>34.837</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>57.2526</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>-0.067184</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
         <v>0.1008</v>
       </c>
-      <c r="AY33" t="n">
-        <v>1953.11131475595</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>324.368324611862</v>
+      <c r="AY34" t="n">
+        <v>1969.03604400994</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>328.732055317204</v>
       </c>
     </row>
   </sheetData>

--- a/results/04-2026/beta/inputs-04-2026.xlsx
+++ b/results/04-2026/beta/inputs-04-2026.xlsx
@@ -4285,7 +4285,7 @@
         <v>3334.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>5072.3</v>
+        <v>4841</v>
       </c>
       <c r="R24" t="n">
         <v>2523.6</v>
@@ -4342,7 +4342,7 @@
         <v>346.267</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-2818.38</v>
+        <v>-2790.624</v>
       </c>
       <c r="AK24" t="n">
         <v>-1458.912</v>
@@ -4443,7 +4443,7 @@
         <v>3371.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>5162.9</v>
+        <v>4900</v>
       </c>
       <c r="R25" t="n">
         <v>2568.6</v>
@@ -4500,7 +4500,7 @@
         <v>344.974</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-2884.272</v>
+        <v>-2824.968</v>
       </c>
       <c r="AK25" t="n">
         <v>-1479.648</v>
@@ -4601,7 +4601,7 @@
         <v>3431</v>
       </c>
       <c r="Q26" t="n">
-        <v>5099.5</v>
+        <v>4857</v>
       </c>
       <c r="R26" t="n">
         <v>2592.7</v>
@@ -4658,7 +4658,7 @@
         <v>342.676</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-2928.42</v>
+        <v>-2853.894</v>
       </c>
       <c r="AK26" t="n">
         <v>-1499.826</v>
@@ -4759,7 +4759,7 @@
         <v>3463.7487875286</v>
       </c>
       <c r="Q27" t="n">
-        <v>5117.7343736848</v>
+        <v>4873.74000509989</v>
       </c>
       <c r="R27" t="n">
         <v>2626.36869158331</v>
@@ -4816,7 +4816,7 @@
         <v>348.008366328366</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-2965.37812484218</v>
+        <v>-2877.34680061199</v>
       </c>
       <c r="AK27" t="n">
         <v>-1519.05824299</v>
@@ -4917,7 +4917,7 @@
         <v>3497.25612764809</v>
       </c>
       <c r="Q28" t="n">
-        <v>5156.07541767194</v>
+        <v>4910.68904204549</v>
       </c>
       <c r="R28" t="n">
         <v>2656.13677457201</v>
@@ -4974,7 +4974,7 @@
         <v>353.222696367226</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-3006.53517496281</v>
+        <v>-2903.60748565745</v>
       </c>
       <c r="AK28" t="n">
         <v>-1538.22665593864</v>
@@ -5075,7 +5075,7 @@
         <v>3528.12789542346</v>
       </c>
       <c r="Q29" t="n">
-        <v>5190.38689030448</v>
+        <v>4941.91607347828</v>
       </c>
       <c r="R29" t="n">
         <v>2684.09748115581</v>
@@ -5132,7 +5132,7 @@
         <v>355.865936362206</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-3046.89953937826</v>
+        <v>-2928.79501416885</v>
       </c>
       <c r="AK29" t="n">
         <v>-1556.54023218234</v>
@@ -5233,7 +5233,7 @@
         <v>3560.36271193125</v>
       </c>
       <c r="Q30" t="n">
-        <v>5447.69456827922</v>
+        <v>5196.10880853816</v>
       </c>
       <c r="R30" t="n">
         <v>2709.61779256644</v>
@@ -5290,7 +5290,7 @@
         <v>356.859779384814</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-3108.60436251145</v>
+        <v>-2975.0327286707</v>
       </c>
       <c r="AK30" t="n">
         <v>-1574.72016081599</v>
@@ -5391,7 +5391,7 @@
         <v>3592.51954751041</v>
       </c>
       <c r="Q31" t="n">
-        <v>5483.42963386668</v>
+        <v>5228.69814047849</v>
       </c>
       <c r="R31" t="n">
         <v>2735.18355114505</v>
@@ -5448,7 +5448,7 @@
         <v>358.739093739241</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-3159.66870515718</v>
+        <v>-3010.43754111942</v>
       </c>
       <c r="AK31" t="n">
         <v>-1592.46633808405</v>
@@ -5549,7 +5549,7 @@
         <v>3623.5322358997</v>
       </c>
       <c r="Q32" t="n">
-        <v>5519.44070620309</v>
+        <v>5261.53239670421</v>
       </c>
       <c r="R32" t="n">
         <v>2761.80377090598</v>
@@ -5606,7 +5606,7 @@
         <v>360.222346635286</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-3190.8019158048</v>
+        <v>-3039.59490021163</v>
       </c>
       <c r="AK32" t="n">
         <v>-1609.88972303878</v>
@@ -5707,7 +5707,7 @@
         <v>3654.41530888475</v>
       </c>
       <c r="Q33" t="n">
-        <v>5554.96361371836</v>
+        <v>5293.62565980728</v>
       </c>
       <c r="R33" t="n">
         <v>2788.75455279793</v>
@@ -5764,7 +5764,7 @@
         <v>367.007979818939</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-3218.617771419</v>
+        <v>-3067.1080909598</v>
       </c>
       <c r="AK33" t="n">
         <v>-1626.31325630583</v>
@@ -5865,7 +5865,7 @@
         <v>3685.16965313856</v>
       </c>
       <c r="Q34" t="n">
-        <v>5638.71752992768</v>
+        <v>5373.91780424032</v>
       </c>
       <c r="R34" t="n">
         <v>2816.33443957647</v>
@@ -5922,7 +5922,7 @@
         <v>375.061936771887</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-3258.12743263814</v>
+        <v>-3104.86628366638</v>
       </c>
       <c r="AK34" t="n">
         <v>-1643.00316280064</v>

--- a/results/04-2026/beta/inputs-04-2026.xlsx
+++ b/results/04-2026/beta/inputs-04-2026.xlsx
@@ -4285,7 +4285,7 @@
         <v>3334.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>4841</v>
+        <v>5072.3</v>
       </c>
       <c r="R24" t="n">
         <v>2523.6</v>
@@ -4342,7 +4342,7 @@
         <v>346.267</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-2790.624</v>
+        <v>-2818.38</v>
       </c>
       <c r="AK24" t="n">
         <v>-1458.912</v>
@@ -4443,7 +4443,7 @@
         <v>3371.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>4900</v>
+        <v>5162.9</v>
       </c>
       <c r="R25" t="n">
         <v>2568.6</v>
@@ -4500,7 +4500,7 @@
         <v>344.974</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-2824.968</v>
+        <v>-2884.272</v>
       </c>
       <c r="AK25" t="n">
         <v>-1479.648</v>
@@ -4601,7 +4601,7 @@
         <v>3431</v>
       </c>
       <c r="Q26" t="n">
-        <v>4857</v>
+        <v>5099.5</v>
       </c>
       <c r="R26" t="n">
         <v>2592.7</v>
@@ -4658,7 +4658,7 @@
         <v>342.676</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-2853.894</v>
+        <v>-2928.42</v>
       </c>
       <c r="AK26" t="n">
         <v>-1499.826</v>
@@ -4759,13 +4759,13 @@
         <v>3463.7487875286</v>
       </c>
       <c r="Q27" t="n">
-        <v>4873.74000509989</v>
+        <v>5047.7343736848</v>
       </c>
       <c r="R27" t="n">
         <v>2626.36869158331</v>
       </c>
       <c r="S27" t="n">
-        <v>432.67747940975</v>
+        <v>357.67747940975</v>
       </c>
       <c r="T27" t="n">
         <v>156.945251003532</v>
@@ -4816,13 +4816,13 @@
         <v>348.008366328366</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-2877.34680061199</v>
+        <v>-2956.97812484218</v>
       </c>
       <c r="AK27" t="n">
         <v>-1519.05824299</v>
       </c>
       <c r="AL27" t="n">
-        <v>-177.366618484671</v>
+        <v>-174.866618484671</v>
       </c>
       <c r="AM27" t="n">
         <v>-70.2697062192393</v>
@@ -4917,13 +4917,13 @@
         <v>3497.25612764809</v>
       </c>
       <c r="Q28" t="n">
-        <v>4910.68904204549</v>
+        <v>5085.41968920096</v>
       </c>
       <c r="R28" t="n">
         <v>2656.13677457201</v>
       </c>
       <c r="S28" t="n">
-        <v>420.676259283967</v>
+        <v>347.756542063329</v>
       </c>
       <c r="T28" t="n">
         <v>164.885835526837</v>
@@ -4974,13 +4974,13 @@
         <v>353.222696367226</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-2903.60748565745</v>
+        <v>-2989.65648754629</v>
       </c>
       <c r="AK28" t="n">
         <v>-1538.22665593864</v>
       </c>
       <c r="AL28" t="n">
-        <v>-177.109160460803</v>
+        <v>-172.178503220115</v>
       </c>
       <c r="AM28" t="n">
         <v>-70.6576510961968</v>
@@ -5075,13 +5075,13 @@
         <v>3528.12789542346</v>
       </c>
       <c r="Q29" t="n">
-        <v>4941.91607347828</v>
+        <v>5119.06929079356</v>
       </c>
       <c r="R29" t="n">
         <v>2684.09748115581</v>
       </c>
       <c r="S29" t="n">
-        <v>439.007918245637</v>
+        <v>443.110782785133</v>
       </c>
       <c r="T29" t="n">
         <v>162.643016309613</v>
@@ -5132,13 +5132,13 @@
         <v>355.865936362206</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-2928.79501416885</v>
+        <v>-3025.66274002043</v>
       </c>
       <c r="AK29" t="n">
         <v>-1556.54023218234</v>
       </c>
       <c r="AL29" t="n">
-        <v>-176.986091068991</v>
+        <v>-172.192195979619</v>
       </c>
       <c r="AM29" t="n">
         <v>-70.9432727516778</v>
@@ -5233,13 +5233,13 @@
         <v>3560.36271193125</v>
       </c>
       <c r="Q30" t="n">
-        <v>5196.10880853816</v>
+        <v>5375.70889761857</v>
       </c>
       <c r="R30" t="n">
         <v>2709.61779256644</v>
       </c>
       <c r="S30" t="n">
-        <v>443.111839208704</v>
+        <v>447.253058026317</v>
       </c>
       <c r="T30" t="n">
         <v>143.140105616203</v>
@@ -5290,13 +5290,13 @@
         <v>356.859779384814</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-2975.0327286707</v>
+        <v>-3082.9686263826</v>
       </c>
       <c r="AK30" t="n">
         <v>-1574.72016081599</v>
       </c>
       <c r="AL30" t="n">
-        <v>-176.013152375948</v>
+        <v>-171.35729791383</v>
       </c>
       <c r="AM30" t="n">
         <v>-71.1937227740491</v>
@@ -5391,13 +5391,13 @@
         <v>3592.51954751041</v>
       </c>
       <c r="Q31" t="n">
-        <v>5228.69814047849</v>
+        <v>5410.76963386668</v>
       </c>
       <c r="R31" t="n">
         <v>2735.18355114505</v>
       </c>
       <c r="S31" t="n">
-        <v>447.254124325517</v>
+        <v>451.434055963587</v>
       </c>
       <c r="T31" t="n">
         <v>115.322937925207</v>
@@ -5448,13 +5448,13 @@
         <v>358.739093739241</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-3010.43754111942</v>
+        <v>-3129.59282499899</v>
       </c>
       <c r="AK31" t="n">
         <v>-1592.46633808405</v>
       </c>
       <c r="AL31" t="n">
-        <v>-174.411623186798</v>
+        <v>-169.895099779283</v>
       </c>
       <c r="AM31" t="n">
         <v>-71.5336735570469</v>
@@ -5549,13 +5549,13 @@
         <v>3623.5322358997</v>
       </c>
       <c r="Q32" t="n">
-        <v>5261.53239670421</v>
+        <v>5446.10006005022</v>
       </c>
       <c r="R32" t="n">
         <v>2761.80377090598</v>
       </c>
       <c r="S32" t="n">
-        <v>451.435132230733</v>
+        <v>455.654138583314</v>
       </c>
       <c r="T32" t="n">
         <v>85.0823596752584</v>
@@ -5606,13 +5606,13 @@
         <v>360.222346635286</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-3039.59490021163</v>
+        <v>-3156.2442983479</v>
       </c>
       <c r="AK32" t="n">
         <v>-1609.88972303878</v>
       </c>
       <c r="AL32" t="n">
-        <v>-173.106127594489</v>
+        <v>-168.73023773206</v>
       </c>
       <c r="AM32" t="n">
         <v>-71.8826222818791</v>
@@ -5707,13 +5707,13 @@
         <v>3654.41530888475</v>
       </c>
       <c r="Q33" t="n">
-        <v>5293.62565980728</v>
+        <v>5480.93594542602</v>
       </c>
       <c r="R33" t="n">
         <v>2788.75455279793</v>
       </c>
       <c r="S33" t="n">
-        <v>455.65522491159</v>
+        <v>459.913671255784</v>
       </c>
       <c r="T33" t="n">
         <v>50.6890505411461</v>
@@ -5764,13 +5764,13 @@
         <v>367.007979818939</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-3067.1080909598</v>
+        <v>-3179.53643376702</v>
       </c>
       <c r="AK33" t="n">
         <v>-1626.31325630583</v>
       </c>
       <c r="AL33" t="n">
-        <v>-171.341301758209</v>
+        <v>-167.107360107253</v>
       </c>
       <c r="AM33" t="n">
         <v>-72.1367489038031</v>
@@ -5865,13 +5865,13 @@
         <v>3685.16965313856</v>
       </c>
       <c r="Q34" t="n">
-        <v>5373.91780424032</v>
+        <v>5563.99640378192</v>
       </c>
       <c r="R34" t="n">
         <v>2816.33443957647</v>
       </c>
       <c r="S34" t="n">
-        <v>459.914767739242</v>
+        <v>464.213022766824</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>375.061936771887</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-3104.86628366638</v>
+        <v>-3214.47999861784</v>
       </c>
       <c r="AK34" t="n">
         <v>-1643.00316280064</v>
       </c>
       <c r="AL34" t="n">
-        <v>-171.031794016184</v>
+        <v>-166.941127532814</v>
       </c>
       <c r="AM34" t="n">
         <v>-72.041206263982</v>

--- a/results/04-2026/beta/inputs-04-2026.xlsx
+++ b/results/04-2026/beta/inputs-04-2026.xlsx
@@ -4765,7 +4765,7 @@
         <v>2626.36869158331</v>
       </c>
       <c r="S27" t="n">
-        <v>357.67747940975</v>
+        <v>132.67747940975</v>
       </c>
       <c r="T27" t="n">
         <v>156.945251003532</v>
@@ -4822,7 +4822,7 @@
         <v>-1519.05824299</v>
       </c>
       <c r="AL27" t="n">
-        <v>-174.866618484671</v>
+        <v>-167.366618484671</v>
       </c>
       <c r="AM27" t="n">
         <v>-70.2697062192393</v>
@@ -4923,7 +4923,7 @@
         <v>2656.13677457201</v>
       </c>
       <c r="S28" t="n">
-        <v>347.756542063329</v>
+        <v>128.997390401414</v>
       </c>
       <c r="T28" t="n">
         <v>164.885835526837</v>
@@ -4980,7 +4980,7 @@
         <v>-1538.22665593864</v>
       </c>
       <c r="AL28" t="n">
-        <v>-172.178503220115</v>
+        <v>-157.386531498051</v>
       </c>
       <c r="AM28" t="n">
         <v>-70.6576510961968</v>
@@ -5081,7 +5081,7 @@
         <v>2684.09748115581</v>
       </c>
       <c r="S29" t="n">
-        <v>443.110782785133</v>
+        <v>455.419376403618</v>
       </c>
       <c r="T29" t="n">
         <v>162.643016309613</v>
@@ -5138,7 +5138,7 @@
         <v>-1556.54023218234</v>
       </c>
       <c r="AL29" t="n">
-        <v>-172.192195979619</v>
+        <v>-157.810510711505</v>
       </c>
       <c r="AM29" t="n">
         <v>-70.9432727516778</v>
@@ -5239,7 +5239,7 @@
         <v>2709.61779256644</v>
       </c>
       <c r="S30" t="n">
-        <v>447.253058026317</v>
+        <v>459.676714479156</v>
       </c>
       <c r="T30" t="n">
         <v>143.140105616203</v>
@@ -5296,7 +5296,7 @@
         <v>-1574.72016081599</v>
       </c>
       <c r="AL30" t="n">
-        <v>-171.35729791383</v>
+        <v>-157.389734527477</v>
       </c>
       <c r="AM30" t="n">
         <v>-71.1937227740491</v>
@@ -5397,7 +5397,7 @@
         <v>2735.18355114505</v>
       </c>
       <c r="S31" t="n">
-        <v>451.434055963587</v>
+        <v>463.973850877797</v>
       </c>
       <c r="T31" t="n">
         <v>115.322937925207</v>
@@ -5454,7 +5454,7 @@
         <v>-1592.46633808405</v>
       </c>
       <c r="AL31" t="n">
-        <v>-169.895099779283</v>
+        <v>-156.345529556737</v>
       </c>
       <c r="AM31" t="n">
         <v>-71.5336735570469</v>
@@ -5555,7 +5555,7 @@
         <v>2761.80377090598</v>
       </c>
       <c r="S32" t="n">
-        <v>455.654138583314</v>
+        <v>468.311157641058</v>
       </c>
       <c r="T32" t="n">
         <v>85.0823596752584</v>
@@ -5612,7 +5612,7 @@
         <v>-1609.88972303878</v>
       </c>
       <c r="AL32" t="n">
-        <v>-168.73023773206</v>
+        <v>-155.602568144772</v>
       </c>
       <c r="AM32" t="n">
         <v>-71.8826222818791</v>
@@ -5713,7 +5713,7 @@
         <v>2788.75455279793</v>
       </c>
       <c r="S33" t="n">
-        <v>459.913671255784</v>
+        <v>472.689010288367</v>
       </c>
       <c r="T33" t="n">
         <v>50.6890505411461</v>
@@ -5770,7 +5770,7 @@
         <v>-1626.31325630583</v>
       </c>
       <c r="AL33" t="n">
-        <v>-167.107360107253</v>
+        <v>-154.405535154384</v>
       </c>
       <c r="AM33" t="n">
         <v>-72.1367489038031</v>
@@ -5871,7 +5871,7 @@
         <v>2816.33443957647</v>
       </c>
       <c r="S34" t="n">
-        <v>464.213022766824</v>
+        <v>477.107787849569</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>-1643.00316280064</v>
       </c>
       <c r="AL34" t="n">
-        <v>-166.941127532814</v>
+        <v>-154.669128082703</v>
       </c>
       <c r="AM34" t="n">
         <v>-72.041206263982</v>

--- a/results/04-2026/beta/inputs-04-2026.xlsx
+++ b/results/04-2026/beta/inputs-04-2026.xlsx
@@ -4273,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1989.7</v>
+        <v>1970.5</v>
       </c>
       <c r="N24" t="n">
         <v>437.306928</v>
@@ -4285,13 +4285,13 @@
         <v>3334.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>5072.3</v>
+        <v>5188</v>
       </c>
       <c r="R24" t="n">
         <v>2523.6</v>
       </c>
       <c r="S24" t="n">
-        <v>208.5</v>
+        <v>508.5</v>
       </c>
       <c r="T24" t="n">
         <v>98.524631049651</v>
@@ -4300,7 +4300,7 @@
         <v>166.7</v>
       </c>
       <c r="V24" t="n">
-        <v>2371.898</v>
+        <v>2371.9</v>
       </c>
       <c r="W24" t="n">
         <v>204</v>
@@ -4342,19 +4342,19 @@
         <v>346.267</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-2818.38</v>
+        <v>-2832.264</v>
       </c>
       <c r="AK24" t="n">
         <v>-1458.912</v>
       </c>
       <c r="AL24" t="n">
-        <v>-174.643333333333</v>
+        <v>-184.643333333333</v>
       </c>
       <c r="AM24" t="n">
         <v>-69.5433333333333</v>
       </c>
       <c r="AN24" t="n">
-        <v>2093.9607</v>
+        <v>2093.96115</v>
       </c>
       <c r="AO24" t="n">
         <v>183.3975</v>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1971.8</v>
+        <v>1942</v>
       </c>
       <c r="N25" t="n">
         <v>417.6033188</v>
@@ -4443,13 +4443,13 @@
         <v>3371.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>5162.9</v>
+        <v>5279</v>
       </c>
       <c r="R25" t="n">
         <v>2568.6</v>
       </c>
       <c r="S25" t="n">
-        <v>458</v>
+        <v>494.4</v>
       </c>
       <c r="T25" t="n">
         <v>110.469375919111</v>
@@ -4458,7 +4458,7 @@
         <v>186.3</v>
       </c>
       <c r="V25" t="n">
-        <v>2375.939</v>
+        <v>2383.2</v>
       </c>
       <c r="W25" t="n">
         <v>205.6</v>
@@ -4500,19 +4500,19 @@
         <v>344.974</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-2884.272</v>
+        <v>-2912.088</v>
       </c>
       <c r="AK25" t="n">
         <v>-1479.648</v>
       </c>
       <c r="AL25" t="n">
-        <v>-175.933333333333</v>
+        <v>-187.146666666666</v>
       </c>
       <c r="AM25" t="n">
         <v>-69.7933333333333</v>
       </c>
       <c r="AN25" t="n">
-        <v>2130.824925</v>
+        <v>2132.4591</v>
       </c>
       <c r="AO25" t="n">
         <v>183.69</v>
@@ -4589,7 +4589,7 @@
         <v>0.06</v>
       </c>
       <c r="M26" t="n">
-        <v>1987.5</v>
+        <v>1942.5</v>
       </c>
       <c r="N26" t="n">
         <v>416.5053188</v>
@@ -4601,13 +4601,13 @@
         <v>3431</v>
       </c>
       <c r="Q26" t="n">
-        <v>5099.5</v>
+        <v>5480</v>
       </c>
       <c r="R26" t="n">
         <v>2592.7</v>
       </c>
       <c r="S26" t="n">
-        <v>445.021075130373</v>
+        <v>480.7</v>
       </c>
       <c r="T26" t="n">
         <v>135.971828422603</v>
@@ -4658,19 +4658,19 @@
         <v>342.676</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-2928.42</v>
+        <v>-2994.954</v>
       </c>
       <c r="AK26" t="n">
         <v>-1499.826</v>
       </c>
       <c r="AL26" t="n">
-        <v>-176.794035837679</v>
+        <v>-189.196666666666</v>
       </c>
       <c r="AM26" t="n">
         <v>-69.9606006263981</v>
       </c>
       <c r="AN26" t="n">
-        <v>2149.252875</v>
+        <v>2150.88705</v>
       </c>
       <c r="AO26" t="n">
         <v>183.7125</v>
@@ -4747,7 +4747,7 @@
         <v>0.06</v>
       </c>
       <c r="M27" t="n">
-        <v>1993.92358728499</v>
+        <v>1938.92358728499</v>
       </c>
       <c r="N27" t="n">
         <v>416.521141931903</v>
@@ -4759,13 +4759,13 @@
         <v>3463.7487875286</v>
       </c>
       <c r="Q27" t="n">
-        <v>5047.7343736848</v>
+        <v>5427.7343736848</v>
       </c>
       <c r="R27" t="n">
         <v>2626.36869158331</v>
       </c>
       <c r="S27" t="n">
-        <v>132.67747940975</v>
+        <v>167.34983588581</v>
       </c>
       <c r="T27" t="n">
         <v>156.945251003532</v>
@@ -4810,25 +4810,25 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2042.95805853092</v>
+        <v>2044.6078654559</v>
       </c>
       <c r="AI27" t="n">
-        <v>348.008366328366</v>
+        <v>346.054179770488</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-2956.97812484218</v>
+        <v>-3062.14612484218</v>
       </c>
       <c r="AK27" t="n">
         <v>-1519.05824299</v>
       </c>
       <c r="AL27" t="n">
-        <v>-167.366618484671</v>
+        <v>-180.924994529527</v>
       </c>
       <c r="AM27" t="n">
         <v>-70.2697062192393</v>
       </c>
       <c r="AN27" t="n">
-        <v>2153.74799957138</v>
+        <v>2155.38217457138</v>
       </c>
       <c r="AO27" t="n">
         <v>189.636056352561</v>
@@ -4861,10 +4861,10 @@
         <v>0.28035</v>
       </c>
       <c r="AY27" t="n">
-        <v>1792.74173816946</v>
+        <v>1793.11294472758</v>
       </c>
       <c r="AZ27" t="n">
-        <v>310.933207423882</v>
+        <v>310.49351544836</v>
       </c>
     </row>
     <row r="28">
@@ -4905,7 +4905,7 @@
         <v>0.06</v>
       </c>
       <c r="M28" t="n">
-        <v>2009.51663900832</v>
+        <v>1948.51663900832</v>
       </c>
       <c r="N28" t="n">
         <v>420.367740074114</v>
@@ -4917,13 +4917,13 @@
         <v>3497.25612764809</v>
       </c>
       <c r="Q28" t="n">
-        <v>5085.41968920096</v>
+        <v>5465.41968920096</v>
       </c>
       <c r="R28" t="n">
         <v>2656.13677457201</v>
       </c>
       <c r="S28" t="n">
-        <v>128.997390401414</v>
+        <v>162.708036129513</v>
       </c>
       <c r="T28" t="n">
         <v>164.885835526837</v>
@@ -4968,25 +4968,25 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2088.12338505647</v>
+        <v>2089.11893503487</v>
       </c>
       <c r="AI28" t="n">
-        <v>353.222696367226</v>
+        <v>351.612487141592</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-2989.65648754629</v>
+        <v>-3117.59448754629</v>
       </c>
       <c r="AK28" t="n">
         <v>-1538.22665593864</v>
       </c>
       <c r="AL28" t="n">
-        <v>-157.386531498051</v>
+        <v>-172.068595733844</v>
       </c>
       <c r="AM28" t="n">
         <v>-70.6576510961968</v>
       </c>
       <c r="AN28" t="n">
-        <v>2171.97389957138</v>
+        <v>2173.60762457138</v>
       </c>
       <c r="AO28" t="n">
         <v>196.194511580697</v>
@@ -5019,10 +5019,10 @@
         <v>0.250425</v>
       </c>
       <c r="AY28" t="n">
-        <v>1826.75957480716</v>
+        <v>1827.35478011042</v>
       </c>
       <c r="AZ28" t="n">
-        <v>312.498239106508</v>
+        <v>311.696250055218</v>
       </c>
     </row>
     <row r="29">
@@ -5063,7 +5063,7 @@
         <v>0.06</v>
       </c>
       <c r="M29" t="n">
-        <v>2021.95019774054</v>
+        <v>1960.75019774054</v>
       </c>
       <c r="N29" t="n">
         <v>422.242386905102</v>
@@ -5075,13 +5075,13 @@
         <v>3528.12789542346</v>
       </c>
       <c r="Q29" t="n">
-        <v>5119.06929079356</v>
+        <v>5499.06929079356</v>
       </c>
       <c r="R29" t="n">
         <v>2684.09748115581</v>
       </c>
       <c r="S29" t="n">
-        <v>455.419376403618</v>
+        <v>488.194986454526</v>
       </c>
       <c r="T29" t="n">
         <v>162.643016309613</v>
@@ -5090,7 +5090,7 @@
         <v>181.26864966443</v>
       </c>
       <c r="V29" t="n">
-        <v>2468.08588813911</v>
+        <v>2476.24088813911</v>
       </c>
       <c r="W29" t="n">
         <v>236.518473484257</v>
@@ -5126,25 +5126,25 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2106.59987078557</v>
+        <v>2122.83581886772</v>
       </c>
       <c r="AI29" t="n">
-        <v>355.865936362206</v>
+        <v>355.685125129242</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-3025.66274002043</v>
+        <v>-3176.40074002043</v>
       </c>
       <c r="AK29" t="n">
         <v>-1556.54023218234</v>
       </c>
       <c r="AL29" t="n">
-        <v>-157.810510711505</v>
+        <v>-173.585095282328</v>
       </c>
       <c r="AM29" t="n">
         <v>-70.9432727516778</v>
       </c>
       <c r="AN29" t="n">
-        <v>2192.70694940268</v>
+        <v>2194.54182440268</v>
       </c>
       <c r="AO29" t="n">
         <v>203.151168114654</v>
@@ -5177,10 +5177,10 @@
         <v>0.222075</v>
       </c>
       <c r="AY29" t="n">
-        <v>1856.36369573392</v>
+        <v>1860.61198935566</v>
       </c>
       <c r="AZ29" t="n">
-        <v>314.948924788005</v>
+        <v>314.106253209297</v>
       </c>
     </row>
     <row r="30">
@@ -5221,7 +5221,7 @@
         <v>0.06</v>
       </c>
       <c r="M30" t="n">
-        <v>2033.28362552671</v>
+        <v>1972.08362552671</v>
       </c>
       <c r="N30" t="n">
         <v>425.1453588</v>
@@ -5233,13 +5233,13 @@
         <v>3560.36271193125</v>
       </c>
       <c r="Q30" t="n">
-        <v>5375.70889761857</v>
+        <v>5847.70889761857</v>
       </c>
       <c r="R30" t="n">
         <v>2709.61779256644</v>
       </c>
       <c r="S30" t="n">
-        <v>459.676714479156</v>
+        <v>492.758716527964</v>
       </c>
       <c r="T30" t="n">
         <v>143.140105616203</v>
@@ -5248,7 +5248,7 @@
         <v>180.713500671141</v>
       </c>
       <c r="V30" t="n">
-        <v>2520.06792730276</v>
+        <v>2528.22292730276</v>
       </c>
       <c r="W30" t="n">
         <v>239.93696178451</v>
@@ -5284,25 +5284,25 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2132.08617923157</v>
+        <v>2147.39142152862</v>
       </c>
       <c r="AI30" t="n">
-        <v>356.859779384814</v>
+        <v>355.886562064553</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-3082.9686263826</v>
+        <v>-3267.5466263826</v>
       </c>
       <c r="AK30" t="n">
         <v>-1574.72016081599</v>
       </c>
       <c r="AL30" t="n">
-        <v>-157.389734527477</v>
+        <v>-174.267052499927</v>
       </c>
       <c r="AM30" t="n">
         <v>-71.1937227740491</v>
       </c>
       <c r="AN30" t="n">
-        <v>2220.9147330458</v>
+        <v>2224.5844830458</v>
       </c>
       <c r="AO30" t="n">
         <v>211.371984516169</v>
@@ -5335,10 +5335,10 @@
         <v>0.1953</v>
       </c>
       <c r="AY30" t="n">
-        <v>1883.19768606102</v>
+        <v>1890.8896591996</v>
       </c>
       <c r="AZ30" t="n">
-        <v>318.140275149588</v>
+        <v>317.078629673822</v>
       </c>
     </row>
     <row r="31">
@@ -5379,7 +5379,7 @@
         <v>0.06</v>
       </c>
       <c r="M31" t="n">
-        <v>2043.8052482434</v>
+        <v>1982.6052482434</v>
       </c>
       <c r="N31" t="n">
         <v>428.076934857179</v>
@@ -5391,13 +5391,13 @@
         <v>3592.51954751041</v>
       </c>
       <c r="Q31" t="n">
-        <v>5410.76963386668</v>
+        <v>5882.76963386668</v>
       </c>
       <c r="R31" t="n">
         <v>2735.18355114505</v>
       </c>
       <c r="S31" t="n">
-        <v>463.973850877797</v>
+        <v>497.365109129205</v>
       </c>
       <c r="T31" t="n">
         <v>115.322937925207</v>
@@ -5406,7 +5406,7 @@
         <v>180.798523489933</v>
       </c>
       <c r="V31" t="n">
-        <v>2543.63743999979</v>
+        <v>2551.79243999979</v>
       </c>
       <c r="W31" t="n">
         <v>243.404858750762</v>
@@ -5442,25 +5442,25 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2157.0933788699</v>
+        <v>2171.49881042277</v>
       </c>
       <c r="AI31" t="n">
-        <v>358.739093739241</v>
+        <v>356.925712306257</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-3129.59282499899</v>
+        <v>-3348.01082499899</v>
       </c>
       <c r="AK31" t="n">
         <v>-1592.46633808405</v>
       </c>
       <c r="AL31" t="n">
-        <v>-156.345529556737</v>
+        <v>-174.3358894709</v>
       </c>
       <c r="AM31" t="n">
         <v>-71.5336735570469</v>
       </c>
       <c r="AN31" t="n">
-        <v>2246.55598247437</v>
+        <v>2252.06060747437</v>
       </c>
       <c r="AO31" t="n">
         <v>214.42702138253</v>
@@ -5493,10 +5493,10 @@
         <v>0.171675</v>
       </c>
       <c r="AY31" t="n">
-        <v>1908.87813313729</v>
+        <v>1919.44012181714</v>
       </c>
       <c r="AZ31" t="n">
-        <v>320.554688817035</v>
+        <v>319.52472449437</v>
       </c>
     </row>
     <row r="32">
@@ -5537,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2054.90434205558</v>
+        <v>1993.70434205558</v>
       </c>
       <c r="N32" t="n">
         <v>431.037396925078</v>
@@ -5549,13 +5549,13 @@
         <v>3623.5322358997</v>
       </c>
       <c r="Q32" t="n">
-        <v>5446.10006005022</v>
+        <v>5918.10006005022</v>
       </c>
       <c r="R32" t="n">
         <v>2761.80377090598</v>
       </c>
       <c r="S32" t="n">
-        <v>468.311157641058</v>
+        <v>502.014563074843</v>
       </c>
       <c r="T32" t="n">
         <v>85.0823596752584</v>
@@ -5564,7 +5564,7 @@
         <v>180.568461744966</v>
       </c>
       <c r="V32" t="n">
-        <v>2567.324392</v>
+        <v>2575.479392</v>
       </c>
       <c r="W32" t="n">
         <v>246.922878504595</v>
@@ -5600,25 +5600,25 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>2183.90946118689</v>
+        <v>2197.00671246076</v>
       </c>
       <c r="AI32" t="n">
-        <v>360.222346635286</v>
+        <v>357.96015353724</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-3156.2442983479</v>
+        <v>-3396.0402983479</v>
       </c>
       <c r="AK32" t="n">
         <v>-1609.88972303878</v>
       </c>
       <c r="AL32" t="n">
-        <v>-155.602568144772</v>
+        <v>-174.716374906729</v>
       </c>
       <c r="AM32" t="n">
         <v>-71.8826222818791</v>
       </c>
       <c r="AN32" t="n">
-        <v>2272.30102067437</v>
+        <v>2279.64052067437</v>
       </c>
       <c r="AO32" t="n">
         <v>217.526213817928</v>
@@ -5651,10 +5651,10 @@
         <v>0.14805</v>
       </c>
       <c r="AY32" t="n">
-        <v>1930.43000026663</v>
+        <v>1943.71487173797</v>
       </c>
       <c r="AZ32" t="n">
-        <v>322.129610127348</v>
+        <v>320.952949433391</v>
       </c>
     </row>
     <row r="33">
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2060.69519681232</v>
+        <v>1999.49519681232</v>
       </c>
       <c r="N33" t="n">
         <v>434.027029629306</v>
@@ -5707,13 +5707,13 @@
         <v>3654.41530888475</v>
       </c>
       <c r="Q33" t="n">
-        <v>5480.93594542602</v>
+        <v>5952.93594542602</v>
       </c>
       <c r="R33" t="n">
         <v>2788.75455279793</v>
       </c>
       <c r="S33" t="n">
-        <v>472.689010288367</v>
+        <v>506.707480909676</v>
       </c>
       <c r="T33" t="n">
         <v>50.6890505411461</v>
@@ -5722,7 +5722,7 @@
         <v>181.823798657718</v>
       </c>
       <c r="V33" t="n">
-        <v>2569.48522454606</v>
+        <v>2599.28522454606</v>
       </c>
       <c r="W33" t="n">
         <v>250.491745489055</v>
@@ -5758,25 +5758,25 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2198.34357500005</v>
+        <v>2213.11319335473</v>
       </c>
       <c r="AI33" t="n">
-        <v>367.007979818939</v>
+        <v>365.49063917812</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-3179.53643376702</v>
+        <v>-3440.68643376702</v>
       </c>
       <c r="AK33" t="n">
         <v>-1626.31325630583</v>
       </c>
       <c r="AL33" t="n">
-        <v>-154.405535154384</v>
+        <v>-174.653290937051</v>
       </c>
       <c r="AM33" t="n">
         <v>-72.1367489038031</v>
       </c>
       <c r="AN33" t="n">
-        <v>2295.11587136594</v>
+        <v>2307.32549636594</v>
       </c>
       <c r="AO33" t="n">
         <v>220.670200019007</v>
@@ -5809,10 +5809,10 @@
         <v>0.124425</v>
       </c>
       <c r="AY33" t="n">
-        <v>1951.07233371489</v>
+        <v>1964.02728099755</v>
       </c>
       <c r="AZ33" t="n">
-        <v>324.636569905113</v>
+        <v>323.159190094388</v>
       </c>
     </row>
     <row r="34">
@@ -5853,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2064.47645564375</v>
+        <v>2003.27645564375</v>
       </c>
       <c r="N34" t="n">
         <v>437.0461204</v>
@@ -5865,13 +5865,13 @@
         <v>3685.16965313856</v>
       </c>
       <c r="Q34" t="n">
-        <v>5563.99640378192</v>
+        <v>6035.99640378192</v>
       </c>
       <c r="R34" t="n">
         <v>2816.33443957647</v>
       </c>
       <c r="S34" t="n">
-        <v>477.107787849569</v>
+        <v>511.444268941559</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
         <v>181.533720805369</v>
       </c>
       <c r="V34" t="n">
-        <v>2594.4113965679</v>
+        <v>2624.2113965679</v>
       </c>
       <c r="W34" t="n">
         <v>254.112194617826</v>
@@ -5916,25 +5916,25 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2211.92489165399</v>
+        <v>2229.38130511742</v>
       </c>
       <c r="AI34" t="n">
-        <v>375.061936771887</v>
+        <v>373.369976667116</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-3214.47999861784</v>
+        <v>-3481.11999861784</v>
       </c>
       <c r="AK34" t="n">
         <v>-1643.00316280064</v>
       </c>
       <c r="AL34" t="n">
-        <v>-154.669128082703</v>
+        <v>-176.061433235103</v>
       </c>
       <c r="AM34" t="n">
         <v>-72.041206263982</v>
       </c>
       <c r="AN34" t="n">
-        <v>2311.84315195059</v>
+        <v>2328.92290195059</v>
       </c>
       <c r="AO34" t="n">
         <v>223.859627406503</v>
@@ -5967,10 +5967,10 @@
         <v>0.1008</v>
       </c>
       <c r="AY34" t="n">
-        <v>1969.03604400994</v>
+        <v>1982.47500480503</v>
       </c>
       <c r="AZ34" t="n">
-        <v>328.732055317204</v>
+        <v>327.092958379965</v>
       </c>
     </row>
   </sheetData>
